--- a/data/trans_orig/IP07B-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07B-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2007 (tasa de respuesta: 87,69%)</t>
+          <t>Menores según su salud general autopercibida en 2007 (tasa de respuesta: 87,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5004</t>
+          <t>4781</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>665</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7761</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11672</t>
+          <t>11900</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23020</t>
+          <t>23009</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15998</t>
+          <t>16286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28965</t>
+          <t>29341</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30141</t>
+          <t>31468</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48452</t>
+          <t>47973</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,45%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24226</t>
+          <t>24027</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35904</t>
+          <t>35414</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25770</t>
+          <t>24952</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39199</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52459</t>
+          <t>52768</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>71138</t>
+          <t>70649</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,1%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11817</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5570</t>
+          <t>5678</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14714</t>
+          <t>14653</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23466</t>
+          <t>23603</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>535</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>5359</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>685</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6608</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1945</t>
+          <t>1900</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9009</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17866</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14077</t>
+          <t>13976</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26809</t>
+          <t>26659</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24243</t>
+          <t>25121</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40600</t>
+          <t>41165</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55438</t>
+          <t>54872</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>69484</t>
+          <t>69542</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45290</t>
+          <t>45534</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59950</t>
+          <t>60079</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>49,55%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104079</t>
+          <t>103251</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125171</t>
+          <t>125647</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,81%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>14411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27023</t>
+          <t>27084</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10717</t>
+          <t>10640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>22778</t>
+          <t>22876</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28959</t>
+          <t>28733</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46308</t>
+          <t>45304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2215,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3482</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3611</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16374</t>
+          <t>16317</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18364</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18300</t>
+          <t>18751</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31641</t>
+          <t>32032</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25359</t>
+          <t>25443</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36604</t>
+          <t>36872</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,77%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33551</t>
+          <t>33435</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45740</t>
+          <t>45051</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>62921</t>
+          <t>62171</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78697</t>
+          <t>79401</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,22%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8200</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4073</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11572</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26153</t>
+          <t>26336</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3340</t>
+          <t>4373</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>5309</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,33%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25194</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>22109</t>
+          <t>20544</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>24858</t>
+          <t>23996</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>41130</t>
+          <t>41138</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31216</t>
+          <t>31488</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45480</t>
+          <t>45545</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>48167</t>
+          <t>48526</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>62494</t>
+          <t>62524</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83479</t>
+          <t>82924</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>104027</t>
+          <t>103475</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>64,95%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>10695</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24846</t>
+          <t>23347</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8756</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>19589</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>23179</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>39936</t>
+          <t>39491</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,79%</t>
         </is>
       </c>
     </row>
@@ -3466,7 +3466,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4532</t>
+          <t>4146</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3203</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11112</t>
+          <t>10069</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>17895</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47481</t>
+          <t>47484</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>70200</t>
+          <t>69797</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>58579</t>
+          <t>58544</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>81319</t>
+          <t>81807</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>112821</t>
+          <t>111046</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>144794</t>
+          <t>142730</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>149058</t>
+          <t>148734</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>175001</t>
+          <t>175311</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>166420</t>
+          <t>165446</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>193474</t>
+          <t>193116</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,91%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>322098</t>
+          <t>324773</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>360250</t>
+          <t>362301</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>55,48%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>46887</t>
+          <t>47379</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>68555</t>
+          <t>68577</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,12 +3928,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>37539</t>
+          <t>37186</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>57591</t>
+          <t>56745</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,12 +3963,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>89947</t>
+          <t>89055</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>118263</t>
+          <t>118681</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,28%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2012 (tasa de respuesta: 90,72%)</t>
+          <t>Menores según su salud general autopercibida en 2012 (tasa de respuesta: 90,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>3267</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4430,7 +4430,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4450,7 +4450,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3440</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4465,7 +4465,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -4493,7 +4493,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5745</t>
+          <t>5657</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1528</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9262</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8155</t>
+          <t>7443</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18767</t>
+          <t>18920</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9405</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20677</t>
+          <t>20807</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20040</t>
+          <t>19421</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35888</t>
+          <t>35223</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28796</t>
+          <t>29157</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41070</t>
+          <t>41915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4729,12 +4729,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4749,12 +4749,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29767</t>
+          <t>29834</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43096</t>
+          <t>43779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4764,12 +4764,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,42%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4784,12 +4784,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>62927</t>
+          <t>63326</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>81351</t>
+          <t>81251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4799,12 +4799,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>64,05%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3986</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12622</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10083</t>
+          <t>9208</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21529</t>
+          <t>21363</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>16096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30282</t>
+          <t>30408</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3366</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5077,7 +5077,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3361</t>
+          <t>3385</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>611</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5252</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1839</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8599</t>
+          <t>8697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3278</t>
+          <t>3339</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11257</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17122</t>
+          <t>17056</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30370</t>
+          <t>29775</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>21499</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>29367</t>
+          <t>29583</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>46996</t>
+          <t>47052</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,08%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43750</t>
+          <t>43282</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>58136</t>
+          <t>57818</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>47,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46009</t>
+          <t>45690</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60981</t>
+          <t>60367</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>67,58%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>93406</t>
+          <t>93068</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114710</t>
+          <t>114492</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,45%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19052</t>
+          <t>19382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12141</t>
+          <t>12580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24407</t>
+          <t>24302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23439</t>
+          <t>23851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>40644</t>
+          <t>39858</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,09%</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4733</t>
+          <t>4555</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3568</t>
+          <t>4161</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5907,7 +5907,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6031</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5942,7 +5942,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>8053</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18104</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,47 +5980,47 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>29,9%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>19522</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>13636</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>25678</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>29,49%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>19522</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>13873</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>25812</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>29,49%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>24423</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39799</t>
+          <t>39697</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29123</t>
+          <t>29527</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41644</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24414</t>
+          <t>24052</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36444</t>
+          <t>37119</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57118</t>
+          <t>56594</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>74652</t>
+          <t>75023</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,5%</t>
+          <t>58,8%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7555</t>
+          <t>7563</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17449</t>
+          <t>17473</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10424</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20982</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>20590</t>
+          <t>20483</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35653</t>
+          <t>35046</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3875</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>594</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>678</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6793</t>
+          <t>6858</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9766</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,65%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19396</t>
+          <t>19009</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>34286</t>
+          <t>33073</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>20497</t>
+          <t>20439</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34641</t>
+          <t>33786</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>43254</t>
+          <t>43276</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>63232</t>
+          <t>65003</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>38,35%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>35996</t>
+          <t>36907</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52484</t>
+          <t>52126</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,78%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34347</t>
+          <t>33929</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>50053</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>74854</t>
+          <t>75297</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>97892</t>
+          <t>97690</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4568</t>
+          <t>4487</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>14823</t>
+          <t>14426</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22239</t>
+          <t>22030</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>17464</t>
+          <t>17074</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33086</t>
+          <t>32772</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,33%</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4477</t>
+          <t>5006</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7143,7 +7143,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>2977</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7158,7 +7158,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>671</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5907</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13598</t>
+          <t>14599</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>6302</t>
+          <t>6558</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>17263</t>
+          <t>16607</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12164</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26548</t>
+          <t>26372</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>61463</t>
+          <t>63296</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>86258</t>
+          <t>86929</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>63508</t>
+          <t>62097</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>88789</t>
+          <t>86620</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>132284</t>
+          <t>131934</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>168315</t>
+          <t>167938</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,78%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>152939</t>
+          <t>153292</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>180187</t>
+          <t>178790</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>61,66%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>147279</t>
+          <t>148479</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>177639</t>
+          <t>175897</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>306806</t>
+          <t>309544</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>347468</t>
+          <t>350592</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>58,0%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>33233</t>
+          <t>32686</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52518</t>
+          <t>52746</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>52329</t>
+          <t>52267</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>75531</t>
+          <t>74765</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>90389</t>
+          <t>90933</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>122218</t>
+          <t>121135</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,04%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2016 (tasa de respuesta: 89,47%)</t>
+          <t>Menores según su salud general autopercibida en 2016 (tasa de respuesta: 89,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7347</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7787</t>
+          <t>8323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5268</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15461</t>
+          <t>15214</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7133</t>
+          <t>6956</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18488</t>
+          <t>18211</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>27,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13903</t>
+          <t>14689</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30023</t>
+          <t>29157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>22,56%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19713</t>
+          <t>20276</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33850</t>
+          <t>34036</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8391,12 +8391,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18444</t>
+          <t>17804</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31680</t>
+          <t>31193</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8406,12 +8406,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41714</t>
+          <t>42077</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61293</t>
+          <t>61395</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,5%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20122</t>
+          <t>19894</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>34096</t>
+          <t>33684</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19767</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33584</t>
+          <t>34062</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43691</t>
+          <t>44019</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63252</t>
+          <t>63407</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,93%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -8739,7 +8739,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3463</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8774,7 +8774,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8817,7 +8817,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4300</t>
+          <t>4214</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8852,7 +8852,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8867,7 +8867,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>547</t>
+          <t>551</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4995</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20599</t>
+          <t>20575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6865</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>17594</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>18595</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34175</t>
+          <t>34769</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41401</t>
+          <t>41260</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56866</t>
+          <t>57536</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>59,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35923</t>
+          <t>35331</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>51503</t>
+          <t>52039</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>81976</t>
+          <t>81727</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>104118</t>
+          <t>104573</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,35%</t>
+          <t>53,58%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25040</t>
+          <t>25440</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>39848</t>
+          <t>40230</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34709</t>
+          <t>33662</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>49787</t>
+          <t>50380</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63176</t>
+          <t>62291</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85406</t>
+          <t>84220</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,15%</t>
         </is>
       </c>
     </row>
@@ -9386,7 +9386,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9401,7 +9401,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3516</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4624</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>653</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5885</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>644</t>
+          <t>643</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9584,7 +9584,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1196</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6717</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6582</t>
+          <t>6164</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16298</t>
+          <t>17091</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>8554</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20219</t>
+          <t>20106</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,1%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27026</t>
+          <t>27166</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39763</t>
+          <t>39288</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18761</t>
+          <t>19151</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32270</t>
+          <t>32703</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>48,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>49779</t>
+          <t>50203</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>68667</t>
+          <t>68032</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19304</t>
+          <t>19739</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>31598</t>
+          <t>32691</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25054</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>37463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47764</t>
+          <t>46621</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>66578</t>
+          <t>65484</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>49,17%</t>
         </is>
       </c>
     </row>
@@ -10181,7 +10181,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3732</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10196,7 +10196,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12601</t>
+          <t>12652</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>26663</t>
+          <t>26043</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>13029</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>26409</t>
+          <t>26542</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>28764</t>
+          <t>28282</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>47719</t>
+          <t>48965</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>43274</t>
+          <t>43056</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60252</t>
+          <t>60011</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>34818</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51460</t>
+          <t>51839</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>55,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>84514</t>
+          <t>82821</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>107343</t>
+          <t>108056</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19604</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35065</t>
+          <t>35094</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,55%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>23637</t>
+          <t>23447</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>39401</t>
+          <t>39914</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>47356</t>
+          <t>46889</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69245</t>
+          <t>68823</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,74%</t>
         </is>
       </c>
     </row>
@@ -10750,7 +10750,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3256</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10765,7 +10765,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10785,7 +10785,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4873</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>656</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5561</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10835,7 +10835,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>9008</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10913,7 +10913,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4888</t>
+          <t>4643</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14688</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37389</t>
+          <t>36801</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>59008</t>
+          <t>57718</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>41890</t>
+          <t>42018</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>63979</t>
+          <t>64677</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>84241</t>
+          <t>83959</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>115265</t>
+          <t>115642</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,79%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>147619</t>
+          <t>146168</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>177654</t>
+          <t>176316</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11099,12 +11099,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>54,8%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>122116</t>
+          <t>121741</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>152581</t>
+          <t>151631</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>279496</t>
+          <t>277304</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>320525</t>
+          <t>320344</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,27%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>96434</t>
+          <t>97139</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>123760</t>
+          <t>125365</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>116209</t>
+          <t>116630</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>146524</t>
+          <t>146405</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>222609</t>
+          <t>220457</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>262948</t>
+          <t>263155</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según salud general autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según su salud general autopercibida en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11777,7 +11777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3354</t>
+          <t>3500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11792,7 +11792,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11847,7 +11847,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3249</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11862,7 +11862,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -11885,12 +11885,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5438</t>
+          <t>5608</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13122</t>
+          <t>13836</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>18407</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37940</t>
+          <t>38260</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11935,12 +11935,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>38,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,01%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>24940</t>
+          <t>25458</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>53584</t>
+          <t>50836</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -11998,12 +11998,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13969</t>
+          <t>13526</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22503</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -12013,12 +12013,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -12033,12 +12033,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8975</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26395</t>
+          <t>26507</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12048,12 +12048,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12068,12 +12068,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23272</t>
+          <t>24123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46644</t>
+          <t>47737</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12083,12 +12083,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>60,28%</t>
         </is>
       </c>
     </row>
@@ -12111,12 +12111,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6497</t>
+          <t>6224</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -12126,12 +12126,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -12146,12 +12146,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>461</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -12161,12 +12161,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -12181,12 +12181,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2403</t>
+          <t>2533</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>10705</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -12196,12 +12196,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -12459,7 +12459,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3999</t>
+          <t>3301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>766</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7147</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>796</t>
+          <t>842</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7608</t>
+          <t>8332</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>11310</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22858</t>
+          <t>23044</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,62%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31390</t>
+          <t>32818</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52924</t>
+          <t>52970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>48955</t>
+          <t>47141</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>71493</t>
+          <t>71586</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,77%</t>
         </is>
       </c>
     </row>
@@ -12680,12 +12680,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22495</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34633</t>
+          <t>34698</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12695,12 +12695,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,57%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12715,12 +12715,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34557</t>
+          <t>34917</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54880</t>
+          <t>54037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12730,12 +12730,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,4%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12750,12 +12750,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61576</t>
+          <t>60029</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84374</t>
+          <t>85655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>54,76%</t>
         </is>
       </c>
     </row>
@@ -12793,12 +12793,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3650</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12005</t>
+          <t>12375</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12808,12 +12808,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12828,12 +12828,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5881</t>
+          <t>6208</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28405</t>
+          <t>29191</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12843,12 +12843,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12863,12 +12863,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12640</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>35221</t>
+          <t>37106</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -13141,7 +13141,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2668</t>
+          <t>3277</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2622</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13226,7 +13226,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24923</t>
+          <t>24756</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13062</t>
+          <t>13467</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30789</t>
+          <t>31132</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17106</t>
+          <t>18779</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>49375</t>
+          <t>48998</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,29%</t>
         </is>
       </c>
     </row>
@@ -13362,12 +13362,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9017</t>
+          <t>8401</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40736</t>
+          <t>39819</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13377,12 +13377,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>55,79%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13397,12 +13397,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21632</t>
+          <t>22012</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40587</t>
+          <t>40722</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13412,12 +13412,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>31184</t>
+          <t>27973</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>71898</t>
+          <t>73187</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,71%</t>
         </is>
       </c>
     </row>
@@ -13475,12 +13475,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10609</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58337</t>
+          <t>58676</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -13490,12 +13490,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -13510,12 +13510,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8232</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21228</t>
+          <t>20730</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13525,12 +13525,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13545,12 +13545,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23967</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88396</t>
+          <t>88778</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13560,12 +13560,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,66%</t>
+          <t>63,93%</t>
         </is>
       </c>
     </row>
@@ -13823,7 +13823,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4518</t>
+          <t>4092</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13838,7 +13838,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>4676</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13873,7 +13873,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>167</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>5448</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12206</t>
+          <t>12221</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>24293</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>7830</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19542</t>
+          <t>18795</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>21756</t>
+          <t>22743</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39331</t>
+          <t>39342</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,81%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>18577</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30474</t>
+          <t>30116</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14079,12 +14079,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>21040</t>
+          <t>21042</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34680</t>
+          <t>34704</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14094,12 +14094,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42692</t>
+          <t>41976</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61998</t>
+          <t>60952</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,86%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6492</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16588</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9401</t>
+          <t>9426</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>21538</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18809</t>
+          <t>18576</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34372</t>
+          <t>33686</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>30,66%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>37688</t>
+          <t>35203</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>70463</t>
+          <t>70919</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>86352</t>
+          <t>86687</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>128183</t>
+          <t>129687</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>129018</t>
+          <t>128469</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>189335</t>
+          <t>187942</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,81%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>56727</t>
+          <t>61605</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>113477</t>
+          <t>112788</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>100832</t>
+          <t>101574</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>139835</t>
+          <t>139047</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14776,12 +14776,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>37,2%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>179936</t>
+          <t>177327</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>242548</t>
+          <t>241772</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14811,12 +14811,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,92%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>30692</t>
+          <t>31647</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>114978</t>
+          <t>105389</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>54,41%</t>
+          <t>49,88%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>32264</t>
+          <t>33669</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>61784</t>
+          <t>61686</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>72309</t>
+          <t>73114</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>181440</t>
+          <t>181935</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,57%</t>
         </is>
       </c>
     </row>
